--- a/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
+++ b/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
@@ -652,7 +652,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Institutional quarterly macro-quant model | formula-driven | point-in-time inputs | 2021-Q1 to 2026-Q4</t>
+          <t>Institutional quarterly macro-quant model | formula-driven | point-in-time inputs | 2021-Q1 to latest available quarter</t>
         </is>
       </c>
     </row>
@@ -1797,11 +1797,11 @@
         <v/>
       </c>
       <c r="P5" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S5,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S5)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S5,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S5)-1)/2)</f>
         <v/>
       </c>
       <c r="Q5" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D5,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D5)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D5,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D5)-1)/2)</f>
         <v/>
       </c>
       <c r="R5" s="30">
@@ -1875,11 +1875,11 @@
         <v/>
       </c>
       <c r="P6" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S6,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S6)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S6,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S6)-1)/2)</f>
         <v/>
       </c>
       <c r="Q6" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D6,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D6)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D6,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D6)-1)/2)</f>
         <v/>
       </c>
       <c r="R6" s="30">
@@ -1953,11 +1953,11 @@
         <v/>
       </c>
       <c r="P7" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S7,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S7)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S7,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S7)-1)/2)</f>
         <v/>
       </c>
       <c r="Q7" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D7,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D7)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D7,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D7)-1)/2)</f>
         <v/>
       </c>
       <c r="R7" s="30">
@@ -2031,11 +2031,11 @@
         <v/>
       </c>
       <c r="P8" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S8,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S8)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S8,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S8)-1)/2)</f>
         <v/>
       </c>
       <c r="Q8" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D8,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D8)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D8,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D8)-1)/2)</f>
         <v/>
       </c>
       <c r="R8" s="30">
@@ -2109,11 +2109,11 @@
         <v/>
       </c>
       <c r="P9" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S9,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S9)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S9,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S9)-1)/2)</f>
         <v/>
       </c>
       <c r="Q9" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D9,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D9)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D9,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D9)-1)/2)</f>
         <v/>
       </c>
       <c r="R9" s="30">
@@ -2187,11 +2187,11 @@
         <v/>
       </c>
       <c r="P10" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S10,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S10)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S10,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S10)-1)/2)</f>
         <v/>
       </c>
       <c r="Q10" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D10,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D10)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D10,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D10)-1)/2)</f>
         <v/>
       </c>
       <c r="R10" s="30">
@@ -2265,11 +2265,11 @@
         <v/>
       </c>
       <c r="P11" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S11,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S11)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S11,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S11)-1)/2)</f>
         <v/>
       </c>
       <c r="Q11" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D11,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D11)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D11,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D11)-1)/2)</f>
         <v/>
       </c>
       <c r="R11" s="30">
@@ -2343,11 +2343,11 @@
         <v/>
       </c>
       <c r="P12" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S12,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S12)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S12,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S12)-1)/2)</f>
         <v/>
       </c>
       <c r="Q12" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D12,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D12)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D12,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D12)-1)/2)</f>
         <v/>
       </c>
       <c r="R12" s="30">
@@ -2421,11 +2421,11 @@
         <v/>
       </c>
       <c r="P13" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S13,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S13)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S13,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S13)-1)/2)</f>
         <v/>
       </c>
       <c r="Q13" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D13,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D13)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D13,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D13)-1)/2)</f>
         <v/>
       </c>
       <c r="R13" s="30">
@@ -2499,11 +2499,11 @@
         <v/>
       </c>
       <c r="P14" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S14,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S14)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S14,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S14)-1)/2)</f>
         <v/>
       </c>
       <c r="Q14" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D14,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D14)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D14,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D14)-1)/2)</f>
         <v/>
       </c>
       <c r="R14" s="30">
@@ -2577,11 +2577,11 @@
         <v/>
       </c>
       <c r="P15" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S15,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S15)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S15,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S15)-1)/2)</f>
         <v/>
       </c>
       <c r="Q15" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D15,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D15)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D15,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D15)-1)/2)</f>
         <v/>
       </c>
       <c r="R15" s="30">
@@ -2655,11 +2655,11 @@
         <v/>
       </c>
       <c r="P16" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S16,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S16)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S16,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S16)-1)/2)</f>
         <v/>
       </c>
       <c r="Q16" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D16,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D16)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D16,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D16)-1)/2)</f>
         <v/>
       </c>
       <c r="R16" s="30">
@@ -2733,11 +2733,11 @@
         <v/>
       </c>
       <c r="P17" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S17,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S17)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S17,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S17)-1)/2)</f>
         <v/>
       </c>
       <c r="Q17" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D17,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D17)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D17,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D17)-1)/2)</f>
         <v/>
       </c>
       <c r="R17" s="30">
@@ -2811,11 +2811,11 @@
         <v/>
       </c>
       <c r="P18" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S18,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S18)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S18,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S18)-1)/2)</f>
         <v/>
       </c>
       <c r="Q18" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D18,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D18)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D18,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D18)-1)/2)</f>
         <v/>
       </c>
       <c r="R18" s="30">
@@ -2889,11 +2889,11 @@
         <v/>
       </c>
       <c r="P19" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S19,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S19)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S19,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S19)-1)/2)</f>
         <v/>
       </c>
       <c r="Q19" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D19,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D19)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D19,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D19)-1)/2)</f>
         <v/>
       </c>
       <c r="R19" s="30">
@@ -2967,11 +2967,11 @@
         <v/>
       </c>
       <c r="P20" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S20,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S20)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S20,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S20)-1)/2)</f>
         <v/>
       </c>
       <c r="Q20" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D20,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D20)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D20,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D20)-1)/2)</f>
         <v/>
       </c>
       <c r="R20" s="30">
@@ -3045,11 +3045,11 @@
         <v/>
       </c>
       <c r="P21" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S21,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S21)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S21,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S21)-1)/2)</f>
         <v/>
       </c>
       <c r="Q21" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D21,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D21)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D21,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D21)-1)/2)</f>
         <v/>
       </c>
       <c r="R21" s="30">
@@ -3123,11 +3123,11 @@
         <v/>
       </c>
       <c r="P22" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S22,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S22)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S22,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S22)-1)/2)</f>
         <v/>
       </c>
       <c r="Q22" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D22,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D22)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D22,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D22)-1)/2)</f>
         <v/>
       </c>
       <c r="R22" s="30">
@@ -3201,11 +3201,11 @@
         <v/>
       </c>
       <c r="P23" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S23,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S23)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S23,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S23)-1)/2)</f>
         <v/>
       </c>
       <c r="Q23" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D23,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D23)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D23,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D23)-1)/2)</f>
         <v/>
       </c>
       <c r="R23" s="30">
@@ -3279,11 +3279,11 @@
         <v/>
       </c>
       <c r="P24" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S24,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S24)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S24,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S24)-1)/2)</f>
         <v/>
       </c>
       <c r="Q24" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D24,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D24)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D24,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D24)-1)/2)</f>
         <v/>
       </c>
       <c r="R24" s="30">
@@ -3357,11 +3357,11 @@
         <v/>
       </c>
       <c r="P25" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S25,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S25)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S25,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S25)-1)/2)</f>
         <v/>
       </c>
       <c r="Q25" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D25,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D25)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D25,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D25)-1)/2)</f>
         <v/>
       </c>
       <c r="R25" s="30">
@@ -3435,11 +3435,11 @@
         <v/>
       </c>
       <c r="P26" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S26,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S26)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S26,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S26)-1)/2)</f>
         <v/>
       </c>
       <c r="Q26" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D26,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D26)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D26,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D26)-1)/2)</f>
         <v/>
       </c>
       <c r="R26" s="30">
@@ -3513,11 +3513,11 @@
         <v/>
       </c>
       <c r="P27" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S27,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S27)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S27,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S27)-1)/2)</f>
         <v/>
       </c>
       <c r="Q27" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D27,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D27)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D27,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D27)-1)/2)</f>
         <v/>
       </c>
       <c r="R27" s="30">
@@ -3591,11 +3591,11 @@
         <v/>
       </c>
       <c r="P28" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ('05_Composite_Calibration'!S28,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S28)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ('05_Composite_Calibration'!S28,'05_Composite_Calibration'!$S$5:$S$27,1)+(COUNTIF('05_Composite_Calibration'!$S$5:$S$27,'05_Composite_Calibration'!S28)-1)/2)</f>
         <v/>
       </c>
       <c r="Q28" s="12">
-        <f>IF(ROW()&gt;27,"",RANK.EQ(D28,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D28)-1)/2)</f>
+        <f>IF(ROW()&gt;=28,"",RANK.EQ(D28,$D$5:$D$27,1)+(COUNTIF($D$5:$D$27,D28)-1)/2)</f>
         <v/>
       </c>
       <c r="R28" s="30">
@@ -4731,7 +4731,7 @@
     <col width="11" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="22" customWidth="1" min="19" max="19"/>
+    <col width="13" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
     <col width="11" customWidth="1" min="22" max="22"/>
@@ -5022,7 +5022,7 @@
       <c r="Q6" s="26" t="n"/>
       <c r="R6" s="26" t="n"/>
       <c r="S6" s="26" t="n">
-        <v>3.52000000000001</v>
+        <v>4</v>
       </c>
       <c r="T6" s="26" t="n"/>
       <c r="U6" s="26" t="n"/>
@@ -5100,7 +5100,7 @@
       <c r="Q7" s="23" t="n"/>
       <c r="R7" s="23" t="n"/>
       <c r="S7" s="23" t="n">
-        <v>0.4799999999999898</v>
+        <v>0</v>
       </c>
       <c r="T7" s="23" t="n"/>
       <c r="U7" s="23" t="n"/>
@@ -5178,7 +5178,7 @@
       <c r="Q8" s="26" t="n"/>
       <c r="R8" s="26" t="n"/>
       <c r="S8" s="26" t="n">
-        <v>14.88</v>
+        <v>15</v>
       </c>
       <c r="T8" s="26" t="n"/>
       <c r="U8" s="26" t="n"/>
@@ -5260,14 +5260,12 @@
         <v>1.724412035726501</v>
       </c>
       <c r="S9" s="23" t="n">
-        <v>1.018435127721588</v>
+        <v>1</v>
       </c>
       <c r="T9" s="23" t="n">
         <v>-0.8927076300128868</v>
       </c>
-      <c r="U9" s="23" t="n">
-        <v>26.43</v>
-      </c>
+      <c r="U9" s="23" t="n"/>
       <c r="V9" s="24" t="n">
         <v>0.33276</v>
       </c>
@@ -5346,14 +5344,12 @@
         <v>1.59290629195095</v>
       </c>
       <c r="S10" s="26" t="n">
-        <v>11.02706675377689</v>
+        <v>11</v>
       </c>
       <c r="T10" s="26" t="n">
         <v>-0.8512428058229228</v>
       </c>
-      <c r="U10" s="26" t="n">
-        <v>33.2</v>
-      </c>
+      <c r="U10" s="26" t="n"/>
       <c r="V10" s="27" t="n">
         <v>-0.076852</v>
       </c>
@@ -5432,14 +5428,12 @@
         <v>-0.1240240212033082</v>
       </c>
       <c r="S11" s="23" t="n">
-        <v>79.9817114506164</v>
+        <v>80</v>
       </c>
       <c r="T11" s="23" t="n">
         <v>-0.3969703305582117</v>
       </c>
-      <c r="U11" s="23" t="n">
-        <v>79.56</v>
-      </c>
+      <c r="U11" s="23" t="n"/>
       <c r="V11" s="24" t="n">
         <v>-0.295489</v>
       </c>
@@ -5518,14 +5512,12 @@
         <v>-0.4172856437916561</v>
       </c>
       <c r="S12" s="26" t="n">
-        <v>54.00804760298109</v>
+        <v>54</v>
       </c>
       <c r="T12" s="26" t="n">
         <v>-0.4208818841813037</v>
       </c>
-      <c r="U12" s="26" t="n">
-        <v>81.59</v>
-      </c>
+      <c r="U12" s="26" t="n"/>
       <c r="V12" s="27" t="n">
         <v>-0.08731899999999999</v>
       </c>
@@ -5604,14 +5596,12 @@
         <v>-1.049413518514857</v>
       </c>
       <c r="S13" s="23" t="n">
-        <v>35.00839441711355</v>
+        <v>35</v>
       </c>
       <c r="T13" s="23" t="n">
         <v>-0.0493596837226597</v>
       </c>
-      <c r="U13" s="23" t="n">
-        <v>96.73999999999999</v>
-      </c>
+      <c r="U13" s="23" t="n"/>
       <c r="V13" s="24" t="n">
         <v>0.192768</v>
       </c>
@@ -5690,14 +5680,12 @@
         <v>-0.7470652616011775</v>
       </c>
       <c r="S14" s="26" t="n">
-        <v>21.01184328094853</v>
+        <v>21</v>
       </c>
       <c r="T14" s="26" t="n">
         <v>-0.007539493466672935</v>
       </c>
-      <c r="U14" s="26" t="n">
-        <v>93.11</v>
-      </c>
+      <c r="U14" s="26" t="n"/>
       <c r="V14" s="27" t="n">
         <v>-0.191478</v>
       </c>
@@ -5776,14 +5764,12 @@
         <v>-0.104551543339823</v>
       </c>
       <c r="S15" s="23" t="n">
-        <v>7.022774326261143</v>
+        <v>7</v>
       </c>
       <c r="T15" s="23" t="n">
         <v>-0.2120636389414922</v>
       </c>
-      <c r="U15" s="23" t="n">
-        <v>83.2</v>
-      </c>
+      <c r="U15" s="23" t="n"/>
       <c r="V15" s="24" t="n">
         <v>0.399685</v>
       </c>
@@ -5862,14 +5848,12 @@
         <v>0.3688640925238618</v>
       </c>
       <c r="S16" s="26" t="n">
-        <v>33.00268263121968</v>
+        <v>33</v>
       </c>
       <c r="T16" s="26" t="n">
         <v>-0.3459510356149464</v>
       </c>
-      <c r="U16" s="26" t="n">
-        <v>72.45999999999999</v>
-      </c>
+      <c r="U16" s="26" t="n"/>
       <c r="V16" s="27" t="n">
         <v>0.288734</v>
       </c>
@@ -5948,14 +5932,12 @@
         <v>0.3929348724985154</v>
       </c>
       <c r="S17" s="23" t="n">
-        <v>10.00431344853263</v>
+        <v>10</v>
       </c>
       <c r="T17" s="23" t="n">
         <v>-0.3352892107915442</v>
       </c>
-      <c r="U17" s="23" t="n">
-        <v>70.76000000000001</v>
-      </c>
+      <c r="U17" s="23" t="n"/>
       <c r="V17" s="24" t="n">
         <v>-0.288754</v>
       </c>
@@ -6034,14 +6016,12 @@
         <v>1.255886961070347</v>
       </c>
       <c r="S18" s="26" t="n">
-        <v>1.97453000488774</v>
+        <v>2</v>
       </c>
       <c r="T18" s="26" t="n">
         <v>-0.6695695077539148</v>
       </c>
-      <c r="U18" s="26" t="n">
-        <v>49.07</v>
-      </c>
+      <c r="U18" s="26" t="n"/>
       <c r="V18" s="27" t="n">
         <v>0.260258</v>
       </c>
@@ -6120,14 +6100,12 @@
         <v>1.466509066811024</v>
       </c>
       <c r="S19" s="23" t="n">
-        <v>19.00625019217618</v>
+        <v>19</v>
       </c>
       <c r="T19" s="23" t="n">
         <v>-0.7854970100166639</v>
       </c>
-      <c r="U19" s="23" t="n">
-        <v>36.35</v>
-      </c>
+      <c r="U19" s="23" t="n"/>
       <c r="V19" s="24" t="n">
         <v>-0.070967</v>
       </c>
@@ -6206,14 +6184,12 @@
         <v>1.385418134890549</v>
       </c>
       <c r="S20" s="26" t="n">
-        <v>2.004346623036881</v>
+        <v>2</v>
       </c>
       <c r="T20" s="26" t="n">
         <v>-0.7752907247895523</v>
       </c>
-      <c r="U20" s="26" t="n">
-        <v>40.25</v>
-      </c>
+      <c r="U20" s="26" t="n"/>
       <c r="V20" s="27" t="n">
         <v>-0.22597</v>
       </c>
@@ -6292,14 +6268,12 @@
         <v>1.568734846260315</v>
       </c>
       <c r="S21" s="23" t="n">
-        <v>7.01873272931104</v>
+        <v>7</v>
       </c>
       <c r="T21" s="23" t="n">
         <v>-0.8231059070010005</v>
       </c>
-      <c r="U21" s="23" t="n">
-        <v>31.14</v>
-      </c>
+      <c r="U21" s="23" t="n"/>
       <c r="V21" s="24" t="n">
         <v>-0.12025</v>
       </c>
@@ -6378,14 +6352,12 @@
         <v>1.621584721505385</v>
       </c>
       <c r="S22" s="26" t="n">
-        <v>9.993337290893038</v>
+        <v>10</v>
       </c>
       <c r="T22" s="26" t="n">
         <v>-0.8493534471665757</v>
       </c>
-      <c r="U22" s="26" t="n">
-        <v>28.1</v>
-      </c>
+      <c r="U22" s="26" t="n"/>
       <c r="V22" s="27" t="n">
         <v>0.19508</v>
       </c>
@@ -6464,14 +6436,12 @@
         <v>1.665186805948611</v>
       </c>
       <c r="S23" s="23" t="n">
-        <v>0.01767050904045675</v>
+        <v>0</v>
       </c>
       <c r="T23" s="23" t="n">
         <v>-0.8714508975744635</v>
       </c>
-      <c r="U23" s="23" t="n">
-        <v>25.96</v>
-      </c>
+      <c r="U23" s="23" t="n"/>
       <c r="V23" s="24" t="n">
         <v>0.436843</v>
       </c>
@@ -6550,14 +6520,12 @@
         <v>2.456627904712017</v>
       </c>
       <c r="S24" s="26" t="n">
-        <v>8.981357831531014</v>
+        <v>9</v>
       </c>
       <c r="T24" s="26" t="n">
         <v>-1.197088543881617</v>
       </c>
-      <c r="U24" s="26" t="n">
-        <v>15.03</v>
-      </c>
+      <c r="U24" s="26" t="n"/>
       <c r="V24" s="27" t="n">
         <v>0.657237</v>
       </c>
@@ -6636,14 +6604,12 @@
         <v>2.416033593503357</v>
       </c>
       <c r="S25" s="23" t="n">
-        <v>0.01004136311512127</v>
+        <v>0</v>
       </c>
       <c r="T25" s="23" t="n">
         <v>-1.365312631189681</v>
       </c>
-      <c r="U25" s="23" t="n">
-        <v>10.75</v>
-      </c>
+      <c r="U25" s="23" t="n"/>
       <c r="V25" s="24" t="n">
         <v>-0.384448</v>
       </c>
@@ -6722,14 +6688,12 @@
         <v>1.971043250704673</v>
       </c>
       <c r="S26" s="26" t="n">
-        <v>53.01168925102914</v>
+        <v>53</v>
       </c>
       <c r="T26" s="26" t="n">
         <v>-1.868489179254161</v>
       </c>
-      <c r="U26" s="26" t="n">
-        <v>11.65</v>
-      </c>
+      <c r="U26" s="26" t="n"/>
       <c r="V26" s="27" t="n">
         <v>0.17381</v>
       </c>
@@ -6808,14 +6772,12 @@
         <v>1.699113859669101</v>
       </c>
       <c r="S27" s="23" t="n">
-        <v>16.01229838483351</v>
+        <v>16</v>
       </c>
       <c r="T27" s="23" t="n">
         <v>-1.891629452375064</v>
       </c>
-      <c r="U27" s="23" t="n">
-        <v>15.33</v>
-      </c>
+      <c r="U27" s="23" t="n"/>
       <c r="V27" s="24" t="n">
         <v>-0.254737</v>
       </c>
@@ -6892,14 +6854,12 @@
         <v>0.6810894520369312</v>
       </c>
       <c r="S28" s="26" t="n">
-        <v>19.97001751480342</v>
+        <v>20</v>
       </c>
       <c r="T28" s="26" t="n">
         <v>-1.250996235356308</v>
       </c>
-      <c r="U28" s="26" t="n">
-        <v>48.64</v>
-      </c>
+      <c r="U28" s="26" t="n"/>
       <c r="V28" s="27" t="n">
         <v>-0.119329</v>
       </c>
@@ -13615,7 +13575,7 @@
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
     <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="25" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -13696,7 +13656,7 @@
         <v>0.1994</v>
       </c>
       <c r="F5" s="32" t="n">
-        <v>-0.0002403999999999996</v>
+        <v>-0.0005</v>
       </c>
       <c r="G5" s="10">
         <f>MIN(10,E5*10)</f>
@@ -13726,7 +13686,7 @@
         <v>0.1933</v>
       </c>
       <c r="F6" s="33" t="n">
-        <v>0.0006207000000000001</v>
+        <v>0.0036</v>
       </c>
       <c r="G6" s="10">
         <f>MIN(10,E6*10)</f>
@@ -13756,7 +13716,7 @@
         <v>0.2073</v>
       </c>
       <c r="F7" s="32" t="n">
-        <v>0.0008616999999999997</v>
+        <v>0.0061</v>
       </c>
       <c r="G7" s="10">
         <f>MIN(10,E7*10)</f>
@@ -13786,7 +13746,7 @@
         <v>0.206</v>
       </c>
       <c r="F8" s="33" t="n">
-        <v>0.0001859999999999999</v>
+        <v>0.0009</v>
       </c>
       <c r="G8" s="10">
         <f>MIN(10,E8*10)</f>
@@ -13816,7 +13776,7 @@
         <v>0.1946</v>
       </c>
       <c r="F9" s="32" t="n">
-        <v>-8.659999999999996e-05</v>
+        <v>0.0001</v>
       </c>
       <c r="G9" s="10">
         <f>MIN(10,E9*10)</f>
@@ -13846,7 +13806,7 @@
         <v>0.2055</v>
       </c>
       <c r="F10" s="33" t="n">
-        <v>-8.849999999999981e-05</v>
+        <v>-0.0005</v>
       </c>
       <c r="G10" s="10">
         <f>MIN(10,E10*10)</f>
@@ -13876,7 +13836,7 @@
         <v>0.1655</v>
       </c>
       <c r="F11" s="32" t="n">
-        <v>0.0005384999999999998</v>
+        <v>0.0032</v>
       </c>
       <c r="G11" s="10">
         <f>MIN(10,E11*10)</f>
@@ -13906,7 +13866,7 @@
         <v>0.1582</v>
       </c>
       <c r="F12" s="33" t="n">
-        <v>-7.920000000000016e-05</v>
+        <v>-0.0002</v>
       </c>
       <c r="G12" s="10">
         <f>MIN(10,E12*10)</f>
@@ -13936,7 +13896,7 @@
         <v>0.1528</v>
       </c>
       <c r="F13" s="32" t="n">
-        <v>3.419999999999988e-05</v>
+        <v>0.0004</v>
       </c>
       <c r="G13" s="10">
         <f>MIN(10,E13*10)</f>
@@ -13966,7 +13926,7 @@
         <v>0.1543</v>
       </c>
       <c r="F14" s="33" t="n">
-        <v>5.27000000000001e-05</v>
+        <v>0.0002</v>
       </c>
       <c r="G14" s="10">
         <f>MIN(10,E14*10)</f>
@@ -13996,7 +13956,7 @@
         <v>0.1574</v>
       </c>
       <c r="F15" s="32" t="n">
-        <v>4.660000000000011e-05</v>
+        <v>0.0005</v>
       </c>
       <c r="G15" s="10">
         <f>MIN(10,E15*10)</f>
@@ -14026,7 +13986,7 @@
         <v>0.1305</v>
       </c>
       <c r="F16" s="33" t="n">
-        <v>5.499999999999972e-06</v>
+        <v>0.0002</v>
       </c>
       <c r="G16" s="10">
         <f>MIN(10,E16*10)</f>
@@ -14056,7 +14016,7 @@
         <v>0.1545</v>
       </c>
       <c r="F17" s="32" t="n">
-        <v>-8.449999999999989e-05</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G17" s="10">
         <f>MIN(10,E17*10)</f>
@@ -14086,7 +14046,7 @@
         <v>0.171</v>
       </c>
       <c r="F18" s="33" t="n">
-        <v>-2.000000000000028e-05</v>
+        <v>-0.0001</v>
       </c>
       <c r="G18" s="10">
         <f>MIN(10,E18*10)</f>
@@ -14116,7 +14076,7 @@
         <v>0.1566</v>
       </c>
       <c r="F19" s="32" t="n">
-        <v>-0.0001836000000000006</v>
+        <v>-0.0012</v>
       </c>
       <c r="G19" s="10">
         <f>MIN(10,E19*10)</f>
@@ -14146,7 +14106,7 @@
         <v>0.151</v>
       </c>
       <c r="F20" s="33" t="n">
-        <v>-4.899999999999949e-05</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G20" s="10">
         <f>MIN(10,E20*10)</f>
@@ -14176,7 +14136,7 @@
         <v>0.1299</v>
       </c>
       <c r="F21" s="32" t="n">
-        <v>-4.789999999999992e-05</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G21" s="10">
         <f>MIN(10,E21*10)</f>
@@ -14206,7 +14166,7 @@
         <v>0.1248</v>
       </c>
       <c r="F22" s="33" t="n">
-        <v>-4.779999999999944e-05</v>
+        <v>-0.0004</v>
       </c>
       <c r="G22" s="10">
         <f>MIN(10,E22*10)</f>
@@ -14236,7 +14196,7 @@
         <v>0.126</v>
       </c>
       <c r="F23" s="32" t="n">
-        <v>7.40000000000002e-05</v>
+        <v>0.0005</v>
       </c>
       <c r="G23" s="10">
         <f>MIN(10,E23*10)</f>
@@ -14266,7 +14226,7 @@
         <v>0.1216</v>
       </c>
       <c r="F24" s="33" t="n">
-        <v>0.0001234000000000002</v>
+        <v>0.001</v>
       </c>
       <c r="G24" s="10">
         <f>MIN(10,E24*10)</f>
@@ -14296,7 +14256,7 @@
         <v>0.1209</v>
       </c>
       <c r="F25" s="32" t="n">
-        <v>-5.790000000000007e-05</v>
+        <v>-0.0002</v>
       </c>
       <c r="G25" s="10">
         <f>MIN(10,E25*10)</f>
@@ -14326,7 +14286,7 @@
         <v>0.1141</v>
       </c>
       <c r="F26" s="33" t="n">
-        <v>6.890000000000001e-05</v>
+        <v>0.0007</v>
       </c>
       <c r="G26" s="10">
         <f>MIN(10,E26*10)</f>
@@ -14356,7 +14316,7 @@
         <v>0.1133</v>
       </c>
       <c r="F27" s="32" t="n">
-        <v>-0.0001213000000000001</v>
+        <v>-0.0004</v>
       </c>
       <c r="G27" s="10">
         <f>MIN(10,E27*10)</f>
@@ -14386,7 +14346,7 @@
         <v>0.1092</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>-0.0001911999999999999</v>
+        <v>-0.0005999999999999999</v>
       </c>
       <c r="G28" s="10">
         <f>MIN(10,E28*10)</f>
@@ -15501,7 +15461,7 @@
         <v/>
       </c>
       <c r="L5" s="10">
-        <f>MIN(100,MAX(0,IF(H5=1,80,IF(H5=-1,20,50))+IF(J5&gt;0.6,(J5-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H5=1,1,IF(H5=-1,-1,0))*30*MAX(0,(J5-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15547,7 +15507,7 @@
         <v/>
       </c>
       <c r="L6" s="10">
-        <f>MIN(100,MAX(0,IF(H6=1,80,IF(H6=-1,20,50))+IF(J6&gt;0.6,(J6-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H6=1,1,IF(H6=-1,-1,0))*30*MAX(0,(J6-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15593,7 +15553,7 @@
         <v/>
       </c>
       <c r="L7" s="10">
-        <f>MIN(100,MAX(0,IF(H7=1,80,IF(H7=-1,20,50))+IF(J7&gt;0.6,(J7-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H7=1,1,IF(H7=-1,-1,0))*30*MAX(0,(J7-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15639,7 +15599,7 @@
         <v/>
       </c>
       <c r="L8" s="10">
-        <f>MIN(100,MAX(0,IF(H8=1,80,IF(H8=-1,20,50))+IF(J8&gt;0.6,(J8-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H8=1,1,IF(H8=-1,-1,0))*30*MAX(0,(J8-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15685,7 +15645,7 @@
         <v/>
       </c>
       <c r="L9" s="10">
-        <f>MIN(100,MAX(0,IF(H9=1,80,IF(H9=-1,20,50))+IF(J9&gt;0.6,(J9-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H9=1,1,IF(H9=-1,-1,0))*30*MAX(0,(J9-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15731,7 +15691,7 @@
         <v/>
       </c>
       <c r="L10" s="10">
-        <f>MIN(100,MAX(0,IF(H10=1,80,IF(H10=-1,20,50))+IF(J10&gt;0.6,(J10-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H10=1,1,IF(H10=-1,-1,0))*30*MAX(0,(J10-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15777,7 +15737,7 @@
         <v/>
       </c>
       <c r="L11" s="10">
-        <f>MIN(100,MAX(0,IF(H11=1,80,IF(H11=-1,20,50))+IF(J11&gt;0.6,(J11-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H11=1,1,IF(H11=-1,-1,0))*30*MAX(0,(J11-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15823,7 +15783,7 @@
         <v/>
       </c>
       <c r="L12" s="10">
-        <f>MIN(100,MAX(0,IF(H12=1,80,IF(H12=-1,20,50))+IF(J12&gt;0.6,(J12-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H12=1,1,IF(H12=-1,-1,0))*30*MAX(0,(J12-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15869,7 +15829,7 @@
         <v/>
       </c>
       <c r="L13" s="10">
-        <f>MIN(100,MAX(0,IF(H13=1,80,IF(H13=-1,20,50))+IF(J13&gt;0.6,(J13-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H13=1,1,IF(H13=-1,-1,0))*30*MAX(0,(J13-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15915,7 +15875,7 @@
         <v/>
       </c>
       <c r="L14" s="10">
-        <f>MIN(100,MAX(0,IF(H14=1,80,IF(H14=-1,20,50))+IF(J14&gt;0.6,(J14-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H14=1,1,IF(H14=-1,-1,0))*30*MAX(0,(J14-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -15961,7 +15921,7 @@
         <v/>
       </c>
       <c r="L15" s="10">
-        <f>MIN(100,MAX(0,IF(H15=1,80,IF(H15=-1,20,50))+IF(J15&gt;0.6,(J15-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H15=1,1,IF(H15=-1,-1,0))*30*MAX(0,(J15-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16007,7 +15967,7 @@
         <v/>
       </c>
       <c r="L16" s="10">
-        <f>MIN(100,MAX(0,IF(H16=1,80,IF(H16=-1,20,50))+IF(J16&gt;0.6,(J16-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H16=1,1,IF(H16=-1,-1,0))*30*MAX(0,(J16-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16053,7 +16013,7 @@
         <v/>
       </c>
       <c r="L17" s="10">
-        <f>MIN(100,MAX(0,IF(H17=1,80,IF(H17=-1,20,50))+IF(J17&gt;0.6,(J17-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H17=1,1,IF(H17=-1,-1,0))*30*MAX(0,(J17-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16099,7 +16059,7 @@
         <v/>
       </c>
       <c r="L18" s="10">
-        <f>MIN(100,MAX(0,IF(H18=1,80,IF(H18=-1,20,50))+IF(J18&gt;0.6,(J18-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H18=1,1,IF(H18=-1,-1,0))*30*MAX(0,(J18-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16145,7 +16105,7 @@
         <v/>
       </c>
       <c r="L19" s="10">
-        <f>MIN(100,MAX(0,IF(H19=1,80,IF(H19=-1,20,50))+IF(J19&gt;0.6,(J19-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H19=1,1,IF(H19=-1,-1,0))*30*MAX(0,(J19-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16191,7 +16151,7 @@
         <v/>
       </c>
       <c r="L20" s="10">
-        <f>MIN(100,MAX(0,IF(H20=1,80,IF(H20=-1,20,50))+IF(J20&gt;0.6,(J20-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H20=1,1,IF(H20=-1,-1,0))*30*MAX(0,(J20-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16237,7 +16197,7 @@
         <v/>
       </c>
       <c r="L21" s="10">
-        <f>MIN(100,MAX(0,IF(H21=1,80,IF(H21=-1,20,50))+IF(J21&gt;0.6,(J21-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H21=1,1,IF(H21=-1,-1,0))*30*MAX(0,(J21-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16283,7 +16243,7 @@
         <v/>
       </c>
       <c r="L22" s="10">
-        <f>MIN(100,MAX(0,IF(H22=1,80,IF(H22=-1,20,50))+IF(J22&gt;0.6,(J22-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H22=1,1,IF(H22=-1,-1,0))*30*MAX(0,(J22-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16329,7 +16289,7 @@
         <v/>
       </c>
       <c r="L23" s="10">
-        <f>MIN(100,MAX(0,IF(H23=1,80,IF(H23=-1,20,50))+IF(J23&gt;0.6,(J23-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H23=1,1,IF(H23=-1,-1,0))*30*MAX(0,(J23-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16375,7 +16335,7 @@
         <v/>
       </c>
       <c r="L24" s="10">
-        <f>MIN(100,MAX(0,IF(H24=1,80,IF(H24=-1,20,50))+IF(J24&gt;0.6,(J24-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H24=1,1,IF(H24=-1,-1,0))*30*MAX(0,(J24-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16421,7 +16381,7 @@
         <v/>
       </c>
       <c r="L25" s="10">
-        <f>MIN(100,MAX(0,IF(H25=1,80,IF(H25=-1,20,50))+IF(J25&gt;0.6,(J25-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H25=1,1,IF(H25=-1,-1,0))*30*MAX(0,(J25-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16467,7 +16427,7 @@
         <v/>
       </c>
       <c r="L26" s="10">
-        <f>MIN(100,MAX(0,IF(H26=1,80,IF(H26=-1,20,50))+IF(J26&gt;0.6,(J26-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H26=1,1,IF(H26=-1,-1,0))*30*MAX(0,(J26-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16513,7 +16473,7 @@
         <v/>
       </c>
       <c r="L27" s="10">
-        <f>MIN(100,MAX(0,IF(H27=1,80,IF(H27=-1,20,50))+IF(J27&gt;0.6,(J27-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H27=1,1,IF(H27=-1,-1,0))*30*MAX(0,(J27-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>
@@ -16559,7 +16519,7 @@
         <v/>
       </c>
       <c r="L28" s="10">
-        <f>MIN(100,MAX(0,IF(H28=1,80,IF(H28=-1,20,50))+IF(J28&gt;0.6,(J28-0.6)*50,0)))</f>
+        <f>MIN(100,MAX(0,50+IF(H28=1,1,IF(H28=-1,-1,0))*30*MAX(0,(J28-1/3)/(1-1/3))))</f>
         <v/>
       </c>
     </row>

--- a/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
+++ b/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
@@ -1,24 +1,24 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="00_Executive_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="01_Model_Config" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="02_Market_Inputs" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="03_Factor_SubScores" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="04_Pillar_Calculation" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="05_Composite_Calibration" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="06_MLR_Regression" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="07_VAR_Granger" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="08_ML_Validation" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="09_Feature_Importance" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="10_Backtest_Efficacy" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="11_Data_Audit_Backfill" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="00_Executive_Dashboard" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_Model_Config" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_Market_Inputs" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_Factor_SubScores" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_Pillar_Calculation" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_Composite_Calibration" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_MLR_Regression" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_VAR_Granger" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_ML_Validation" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Feature_Importance" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Backtest_Efficacy" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Data_Audit_Backfill" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_Market_Inputs'!$A$4:$Z$28</definedName>
@@ -980,7 +980,7 @@
       </c>
       <c r="C22" s="15" t="inlineStr">
         <is>
-          <t>≈ 4.56%</t>
+          <t>≈ 5.74%</t>
         </is>
       </c>
       <c r="D22" s="15" t="inlineStr">
@@ -1022,7 +1022,7 @@
       </c>
       <c r="C24" s="15" t="inlineStr">
         <is>
-          <t>≈ 7.34%</t>
+          <t>≈ 7.70%</t>
         </is>
       </c>
       <c r="D24" s="15" t="inlineStr">
@@ -1043,7 +1043,7 @@
       </c>
       <c r="C25" s="16" t="inlineStr">
         <is>
-          <t>≈ 0.01</t>
+          <t>≈ 0.16</t>
         </is>
       </c>
       <c r="D25" s="16" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="C26" s="15" t="inlineStr">
         <is>
-          <t>≈ 0.2372</t>
+          <t>≈ 0.1927</t>
         </is>
       </c>
       <c r="D26" s="15" t="inlineStr">
@@ -4082,7 +4082,7 @@
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>Rounded pillars and weighted legs reproduce production scorer; calibration uses STDEV.S</t>
+          <t>Rounded pillars and weighted legs reproduce production scorer; v2 calibration uses STDEV.S with σ-floor, z winsorisation and distance guardrail</t>
         </is>
       </c>
       <c r="E12" s="15" t="inlineStr">
@@ -4104,12 +4104,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G36"/>
+  <dimension ref="A1:G42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="29" customWidth="1" min="3" max="3"/>
+    <col width="42" customWidth="1" min="3" max="3"/>
     <col width="41" customWidth="1" min="4" max="4"/>
     <col width="22" customWidth="1" min="5" max="5"/>
     <col width="18" customWidth="1" min="6" max="6"/>
@@ -4501,7 +4501,7 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>3. EXPANDING CALIBRATION PARAMETERS</t>
+          <t>3. EXPANDING CALIBRATION PARAMETERS (v2 — winsorized, guard-railed)</t>
         </is>
       </c>
     </row>
@@ -4694,6 +4694,76 @@
       <c r="C36" s="15" t="inlineStr">
         <is>
           <t>Annual Sharpe hurdle</t>
+        </is>
+      </c>
+    </row>
+    <row r="37"/>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>5. CALIBRATION v2 ROBUSTNESS GUARDS</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="32" customHeight="1">
+      <c r="A39" s="7" t="inlineStr">
+        <is>
+          <t>Parameter</t>
+        </is>
+      </c>
+      <c r="B39" s="7" t="inlineStr">
+        <is>
+          <t>Value</t>
+        </is>
+      </c>
+      <c r="C39" s="7" t="inlineStr">
+        <is>
+          <t>Role</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="13" t="inlineStr">
+        <is>
+          <t>min_std</t>
+        </is>
+      </c>
+      <c r="B40" s="13" t="n">
+        <v>5</v>
+      </c>
+      <c r="C40" s="15" t="inlineStr">
+        <is>
+          <t>σ prior floor: tiny-sample σ cannot inflate z (floor ≈ long-run composite dispersion)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>z_cap</t>
+        </is>
+      </c>
+      <c r="B41" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="C41" s="16" t="inlineStr">
+        <is>
+          <t>Winsorise z at ±3σ → response saturates near 5/95; 0/100 unreachable</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="13" t="inlineStr">
+        <is>
+          <t>max_dist_from_raw</t>
+        </is>
+      </c>
+      <c r="B42" s="13" t="n">
+        <v>25</v>
+      </c>
+      <c r="C42" s="15" t="inlineStr">
+        <is>
+          <t>Action signal may not deviate more than ±25 pts from the raw composite</t>
         </is>
       </c>
     </row>
@@ -11573,14 +11643,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>TWO-TIER COMPOSITE &amp; EXPANDING CALIBRATION</t>
+          <t>TWO-TIER COMPOSITE &amp; EXPANDING CALIBRATION (v2)</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>N&lt;4: calibrated = raw | N≥4: clip(50 + 15 × (Raw−μprior)/σprior, 0, 100); prior quarters only</t>
+          <t>N&lt;4: calibrated = raw | N≥4: σeff=MAX(σprior, min_std)·z capped ±z_cap·cal = clip(50+15×z_eff, Raw∓max_dist, 0..100); prior quarters only</t>
         </is>
       </c>
     </row>
@@ -11716,11 +11786,11 @@
         <v/>
       </c>
       <c r="I5" s="31">
-        <f>IF(F5&lt;'01_Model_Config'!$B$26,"",(D5-G5)/H5)</f>
+        <f>IF(F5&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D5-G5)/MAX(H5,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J5" s="10">
-        <f>ROUND(IF(F5&lt;'01_Model_Config'!$B$26,D5,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I5))),2)</f>
+        <f>ROUND(IF(F5&lt;'01_Model_Config'!$B$26,D5,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D5+'01_Model_Config'!$B$42,MAX(D5-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I5))))),2)</f>
         <v/>
       </c>
       <c r="K5" s="12">
@@ -11794,11 +11864,11 @@
         <v/>
       </c>
       <c r="I6" s="31">
-        <f>IF(F6&lt;'01_Model_Config'!$B$26,"",(D6-G6)/H6)</f>
+        <f>IF(F6&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D6-G6)/MAX(H6,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J6" s="10">
-        <f>ROUND(IF(F6&lt;'01_Model_Config'!$B$26,D6,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I6))),2)</f>
+        <f>ROUND(IF(F6&lt;'01_Model_Config'!$B$26,D6,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D6+'01_Model_Config'!$B$42,MAX(D6-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I6))))),2)</f>
         <v/>
       </c>
       <c r="K6" s="12">
@@ -11872,11 +11942,11 @@
         <v/>
       </c>
       <c r="I7" s="31">
-        <f>IF(F7&lt;'01_Model_Config'!$B$26,"",(D7-G7)/H7)</f>
+        <f>IF(F7&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D7-G7)/MAX(H7,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J7" s="10">
-        <f>ROUND(IF(F7&lt;'01_Model_Config'!$B$26,D7,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I7))),2)</f>
+        <f>ROUND(IF(F7&lt;'01_Model_Config'!$B$26,D7,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D7+'01_Model_Config'!$B$42,MAX(D7-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I7))))),2)</f>
         <v/>
       </c>
       <c r="K7" s="12">
@@ -11950,11 +12020,11 @@
         <v/>
       </c>
       <c r="I8" s="31">
-        <f>IF(F8&lt;'01_Model_Config'!$B$26,"",(D8-G8)/H8)</f>
+        <f>IF(F8&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D8-G8)/MAX(H8,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J8" s="10">
-        <f>ROUND(IF(F8&lt;'01_Model_Config'!$B$26,D8,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I8))),2)</f>
+        <f>ROUND(IF(F8&lt;'01_Model_Config'!$B$26,D8,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D8+'01_Model_Config'!$B$42,MAX(D8-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I8))))),2)</f>
         <v/>
       </c>
       <c r="K8" s="12">
@@ -12028,11 +12098,11 @@
         <v/>
       </c>
       <c r="I9" s="31">
-        <f>IF(F9&lt;'01_Model_Config'!$B$26,"",(D9-G9)/H9)</f>
+        <f>IF(F9&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D9-G9)/MAX(H9,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J9" s="10">
-        <f>ROUND(IF(F9&lt;'01_Model_Config'!$B$26,D9,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I9))),2)</f>
+        <f>ROUND(IF(F9&lt;'01_Model_Config'!$B$26,D9,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D9+'01_Model_Config'!$B$42,MAX(D9-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I9))))),2)</f>
         <v/>
       </c>
       <c r="K9" s="12">
@@ -12106,11 +12176,11 @@
         <v/>
       </c>
       <c r="I10" s="31">
-        <f>IF(F10&lt;'01_Model_Config'!$B$26,"",(D10-G10)/H10)</f>
+        <f>IF(F10&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D10-G10)/MAX(H10,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J10" s="10">
-        <f>ROUND(IF(F10&lt;'01_Model_Config'!$B$26,D10,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I10))),2)</f>
+        <f>ROUND(IF(F10&lt;'01_Model_Config'!$B$26,D10,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D10+'01_Model_Config'!$B$42,MAX(D10-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I10))))),2)</f>
         <v/>
       </c>
       <c r="K10" s="12">
@@ -12184,11 +12254,11 @@
         <v/>
       </c>
       <c r="I11" s="31">
-        <f>IF(F11&lt;'01_Model_Config'!$B$26,"",(D11-G11)/H11)</f>
+        <f>IF(F11&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D11-G11)/MAX(H11,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J11" s="10">
-        <f>ROUND(IF(F11&lt;'01_Model_Config'!$B$26,D11,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I11))),2)</f>
+        <f>ROUND(IF(F11&lt;'01_Model_Config'!$B$26,D11,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D11+'01_Model_Config'!$B$42,MAX(D11-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I11))))),2)</f>
         <v/>
       </c>
       <c r="K11" s="12">
@@ -12262,11 +12332,11 @@
         <v/>
       </c>
       <c r="I12" s="31">
-        <f>IF(F12&lt;'01_Model_Config'!$B$26,"",(D12-G12)/H12)</f>
+        <f>IF(F12&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D12-G12)/MAX(H12,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J12" s="10">
-        <f>ROUND(IF(F12&lt;'01_Model_Config'!$B$26,D12,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I12))),2)</f>
+        <f>ROUND(IF(F12&lt;'01_Model_Config'!$B$26,D12,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D12+'01_Model_Config'!$B$42,MAX(D12-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I12))))),2)</f>
         <v/>
       </c>
       <c r="K12" s="12">
@@ -12340,11 +12410,11 @@
         <v/>
       </c>
       <c r="I13" s="31">
-        <f>IF(F13&lt;'01_Model_Config'!$B$26,"",(D13-G13)/H13)</f>
+        <f>IF(F13&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D13-G13)/MAX(H13,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J13" s="10">
-        <f>ROUND(IF(F13&lt;'01_Model_Config'!$B$26,D13,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I13))),2)</f>
+        <f>ROUND(IF(F13&lt;'01_Model_Config'!$B$26,D13,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D13+'01_Model_Config'!$B$42,MAX(D13-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I13))))),2)</f>
         <v/>
       </c>
       <c r="K13" s="12">
@@ -12418,11 +12488,11 @@
         <v/>
       </c>
       <c r="I14" s="31">
-        <f>IF(F14&lt;'01_Model_Config'!$B$26,"",(D14-G14)/H14)</f>
+        <f>IF(F14&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D14-G14)/MAX(H14,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J14" s="10">
-        <f>ROUND(IF(F14&lt;'01_Model_Config'!$B$26,D14,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I14))),2)</f>
+        <f>ROUND(IF(F14&lt;'01_Model_Config'!$B$26,D14,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D14+'01_Model_Config'!$B$42,MAX(D14-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I14))))),2)</f>
         <v/>
       </c>
       <c r="K14" s="12">
@@ -12496,11 +12566,11 @@
         <v/>
       </c>
       <c r="I15" s="31">
-        <f>IF(F15&lt;'01_Model_Config'!$B$26,"",(D15-G15)/H15)</f>
+        <f>IF(F15&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D15-G15)/MAX(H15,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J15" s="10">
-        <f>ROUND(IF(F15&lt;'01_Model_Config'!$B$26,D15,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I15))),2)</f>
+        <f>ROUND(IF(F15&lt;'01_Model_Config'!$B$26,D15,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D15+'01_Model_Config'!$B$42,MAX(D15-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I15))))),2)</f>
         <v/>
       </c>
       <c r="K15" s="12">
@@ -12574,11 +12644,11 @@
         <v/>
       </c>
       <c r="I16" s="31">
-        <f>IF(F16&lt;'01_Model_Config'!$B$26,"",(D16-G16)/H16)</f>
+        <f>IF(F16&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D16-G16)/MAX(H16,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J16" s="10">
-        <f>ROUND(IF(F16&lt;'01_Model_Config'!$B$26,D16,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I16))),2)</f>
+        <f>ROUND(IF(F16&lt;'01_Model_Config'!$B$26,D16,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D16+'01_Model_Config'!$B$42,MAX(D16-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I16))))),2)</f>
         <v/>
       </c>
       <c r="K16" s="12">
@@ -12652,11 +12722,11 @@
         <v/>
       </c>
       <c r="I17" s="31">
-        <f>IF(F17&lt;'01_Model_Config'!$B$26,"",(D17-G17)/H17)</f>
+        <f>IF(F17&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D17-G17)/MAX(H17,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J17" s="10">
-        <f>ROUND(IF(F17&lt;'01_Model_Config'!$B$26,D17,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I17))),2)</f>
+        <f>ROUND(IF(F17&lt;'01_Model_Config'!$B$26,D17,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D17+'01_Model_Config'!$B$42,MAX(D17-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I17))))),2)</f>
         <v/>
       </c>
       <c r="K17" s="12">
@@ -12730,11 +12800,11 @@
         <v/>
       </c>
       <c r="I18" s="31">
-        <f>IF(F18&lt;'01_Model_Config'!$B$26,"",(D18-G18)/H18)</f>
+        <f>IF(F18&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D18-G18)/MAX(H18,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J18" s="10">
-        <f>ROUND(IF(F18&lt;'01_Model_Config'!$B$26,D18,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I18))),2)</f>
+        <f>ROUND(IF(F18&lt;'01_Model_Config'!$B$26,D18,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D18+'01_Model_Config'!$B$42,MAX(D18-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I18))))),2)</f>
         <v/>
       </c>
       <c r="K18" s="12">
@@ -12808,11 +12878,11 @@
         <v/>
       </c>
       <c r="I19" s="31">
-        <f>IF(F19&lt;'01_Model_Config'!$B$26,"",(D19-G19)/H19)</f>
+        <f>IF(F19&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D19-G19)/MAX(H19,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J19" s="10">
-        <f>ROUND(IF(F19&lt;'01_Model_Config'!$B$26,D19,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I19))),2)</f>
+        <f>ROUND(IF(F19&lt;'01_Model_Config'!$B$26,D19,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D19+'01_Model_Config'!$B$42,MAX(D19-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I19))))),2)</f>
         <v/>
       </c>
       <c r="K19" s="12">
@@ -12886,11 +12956,11 @@
         <v/>
       </c>
       <c r="I20" s="31">
-        <f>IF(F20&lt;'01_Model_Config'!$B$26,"",(D20-G20)/H20)</f>
+        <f>IF(F20&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D20-G20)/MAX(H20,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J20" s="10">
-        <f>ROUND(IF(F20&lt;'01_Model_Config'!$B$26,D20,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I20))),2)</f>
+        <f>ROUND(IF(F20&lt;'01_Model_Config'!$B$26,D20,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D20+'01_Model_Config'!$B$42,MAX(D20-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I20))))),2)</f>
         <v/>
       </c>
       <c r="K20" s="12">
@@ -12964,11 +13034,11 @@
         <v/>
       </c>
       <c r="I21" s="31">
-        <f>IF(F21&lt;'01_Model_Config'!$B$26,"",(D21-G21)/H21)</f>
+        <f>IF(F21&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D21-G21)/MAX(H21,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J21" s="10">
-        <f>ROUND(IF(F21&lt;'01_Model_Config'!$B$26,D21,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I21))),2)</f>
+        <f>ROUND(IF(F21&lt;'01_Model_Config'!$B$26,D21,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D21+'01_Model_Config'!$B$42,MAX(D21-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I21))))),2)</f>
         <v/>
       </c>
       <c r="K21" s="12">
@@ -13042,11 +13112,11 @@
         <v/>
       </c>
       <c r="I22" s="31">
-        <f>IF(F22&lt;'01_Model_Config'!$B$26,"",(D22-G22)/H22)</f>
+        <f>IF(F22&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D22-G22)/MAX(H22,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J22" s="10">
-        <f>ROUND(IF(F22&lt;'01_Model_Config'!$B$26,D22,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I22))),2)</f>
+        <f>ROUND(IF(F22&lt;'01_Model_Config'!$B$26,D22,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D22+'01_Model_Config'!$B$42,MAX(D22-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I22))))),2)</f>
         <v/>
       </c>
       <c r="K22" s="12">
@@ -13120,11 +13190,11 @@
         <v/>
       </c>
       <c r="I23" s="31">
-        <f>IF(F23&lt;'01_Model_Config'!$B$26,"",(D23-G23)/H23)</f>
+        <f>IF(F23&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D23-G23)/MAX(H23,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J23" s="10">
-        <f>ROUND(IF(F23&lt;'01_Model_Config'!$B$26,D23,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I23))),2)</f>
+        <f>ROUND(IF(F23&lt;'01_Model_Config'!$B$26,D23,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D23+'01_Model_Config'!$B$42,MAX(D23-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I23))))),2)</f>
         <v/>
       </c>
       <c r="K23" s="12">
@@ -13198,11 +13268,11 @@
         <v/>
       </c>
       <c r="I24" s="31">
-        <f>IF(F24&lt;'01_Model_Config'!$B$26,"",(D24-G24)/H24)</f>
+        <f>IF(F24&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D24-G24)/MAX(H24,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J24" s="10">
-        <f>ROUND(IF(F24&lt;'01_Model_Config'!$B$26,D24,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I24))),2)</f>
+        <f>ROUND(IF(F24&lt;'01_Model_Config'!$B$26,D24,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D24+'01_Model_Config'!$B$42,MAX(D24-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I24))))),2)</f>
         <v/>
       </c>
       <c r="K24" s="12">
@@ -13276,11 +13346,11 @@
         <v/>
       </c>
       <c r="I25" s="31">
-        <f>IF(F25&lt;'01_Model_Config'!$B$26,"",(D25-G25)/H25)</f>
+        <f>IF(F25&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D25-G25)/MAX(H25,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J25" s="10">
-        <f>ROUND(IF(F25&lt;'01_Model_Config'!$B$26,D25,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I25))),2)</f>
+        <f>ROUND(IF(F25&lt;'01_Model_Config'!$B$26,D25,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D25+'01_Model_Config'!$B$42,MAX(D25-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I25))))),2)</f>
         <v/>
       </c>
       <c r="K25" s="12">
@@ -13354,11 +13424,11 @@
         <v/>
       </c>
       <c r="I26" s="31">
-        <f>IF(F26&lt;'01_Model_Config'!$B$26,"",(D26-G26)/H26)</f>
+        <f>IF(F26&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D26-G26)/MAX(H26,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J26" s="10">
-        <f>ROUND(IF(F26&lt;'01_Model_Config'!$B$26,D26,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I26))),2)</f>
+        <f>ROUND(IF(F26&lt;'01_Model_Config'!$B$26,D26,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D26+'01_Model_Config'!$B$42,MAX(D26-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I26))))),2)</f>
         <v/>
       </c>
       <c r="K26" s="12">
@@ -13432,11 +13502,11 @@
         <v/>
       </c>
       <c r="I27" s="31">
-        <f>IF(F27&lt;'01_Model_Config'!$B$26,"",(D27-G27)/H27)</f>
+        <f>IF(F27&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D27-G27)/MAX(H27,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J27" s="10">
-        <f>ROUND(IF(F27&lt;'01_Model_Config'!$B$26,D27,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I27))),2)</f>
+        <f>ROUND(IF(F27&lt;'01_Model_Config'!$B$26,D27,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D27+'01_Model_Config'!$B$42,MAX(D27-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I27))))),2)</f>
         <v/>
       </c>
       <c r="K27" s="12">
@@ -13510,11 +13580,11 @@
         <v/>
       </c>
       <c r="I28" s="31">
-        <f>IF(F28&lt;'01_Model_Config'!$B$26,"",(D28-G28)/H28)</f>
+        <f>IF(F28&lt;'01_Model_Config'!$B$26,"",MIN('01_Model_Config'!$B$41,MAX(-'01_Model_Config'!$B$41,(D28-G28)/MAX(H28,'01_Model_Config'!$B$40))))</f>
         <v/>
       </c>
       <c r="J28" s="10">
-        <f>ROUND(IF(F28&lt;'01_Model_Config'!$B$26,D28,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I28))),2)</f>
+        <f>ROUND(IF(F28&lt;'01_Model_Config'!$B$26,D28,MIN('01_Model_Config'!$B$28,MAX('01_Model_Config'!$B$27,MIN(D28+'01_Model_Config'!$B$42,MAX(D28-'01_Model_Config'!$B$42,'01_Model_Config'!$B$24+'01_Model_Config'!$B$25*I28))))),2)</f>
         <v/>
       </c>
       <c r="K28" s="12">

--- a/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
+++ b/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
@@ -19,6 +19,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_Feature_Importance" sheetId="10" state="visible" r:id="rId10"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_Backtest_Efficacy" sheetId="11" state="visible" r:id="rId11"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_Data_Audit_Backfill" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_Methodology_EN" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_Phuong_Phap_Luan_VN" sheetId="14" state="visible" r:id="rId14"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'02_Market_Inputs'!$A$4:$Z$28</definedName>
@@ -35,7 +37,7 @@
     <numFmt numFmtId="166" formatCode="0.0000%"/>
     <numFmt numFmtId="167" formatCode="0.000000"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="9">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -81,6 +83,12 @@
     </font>
     <font>
       <name val="Calibri"/>
+      <color rgb="001E293B"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
       <color rgb="001E293B"/>
       <sz val="9"/>
     </font>
@@ -158,7 +166,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -264,6 +272,21 @@
     </xf>
     <xf numFmtId="4" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="0" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -4097,6 +4120,518 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00047857"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>VN-INDEX QUANTITATIVE MODEL — METHODOLOGY &amp; INTERPRETATION</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>English guide | scope, point-in-time discipline, architecture, calibration, validation and audit</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>LIVE SNAPSHOT — FORMULA-LINKED TO THE EXECUTIVE DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Latest quarter</t>
+        </is>
+      </c>
+      <c r="B5" s="39">
+        <f>'00_Executive_Dashboard'!A6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Calibrated action</t>
+        </is>
+      </c>
+      <c r="B6" s="39">
+        <f>'00_Executive_Dashboard'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Calibrated score</t>
+        </is>
+      </c>
+      <c r="B7" s="40">
+        <f>'00_Executive_Dashboard'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Equity allocation</t>
+        </is>
+      </c>
+      <c r="B8" s="39">
+        <f>'00_Executive_Dashboard'!D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Raw composite</t>
+        </is>
+      </c>
+      <c r="B9" s="40">
+        <f>'00_Executive_Dashboard'!E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>1. What the model produces</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>The output is a quarterly allocation-regime score and an associated portfolio action. It is NOT a forecast of returns and NOT a probability of a market crash. It is a disciplined decision aid, not investment advice.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>2. Data and point-in-time discipline</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Inputs use VN-Index OHLCV, HOSE market capitalization, VNDirect api-finfo v4 foreign flows for STOCK_HOSE and ETF_HOSE, ADTV, a Nelson-Siegel fitted Vietnam government-bond yield curve, and M2 from ADB KIDB (SBV source) joined to GSO releases.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Each quarter uses only information available at its decision date. If a required source fails, publication stops; the model does not silently substitute fabricated or default data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>3. Six-pillar architecture</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>Macro &amp; Monetary 25%; Global &amp; Intermarket 20%; Valuation &amp; Leverage 20%; Econometric Models 15%; Machine Learning 10%; Market Structure 10%. The weighted legs sum to the raw composite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>4. Calibration v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>After four initial quarters that retain the raw score, calibration uses prior history only: z = (raw − prior_mean) / max(prior_std, min_std); z is winsorised at ±z_cap; calibrated = center + z_scale × z; the result is clipped to [clip_low, clip_high] and constrained to max_dist_from_raw from the raw score.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>SCORE_CALIBRATION parameters are center 50, z_scale 15, min_history 4, min_std 5.0, z_cap 3.0, max_dist_from_raw 25.0, and clip 0–100. The min_std floor prevents unstable small-sample dispersion from magnifying z; z_cap limits outlier leverage; max_dist_from_raw prevents the action signal from moving implausibly far from the raw evidence. These v2 safeguards address the 2022-Q2 collapse to 0.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>5. Action bands</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>80–100 BUY (85–100% equities); 65–79.99 ACCUMULATE (70–85%); 50–64.99 HOLD (40–60%); 35–49.99 REDUCE (20–40%); 0–34.99 SELL (0–20%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>6. Validation and backtest</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>Sheets 06–09 expose regression, VAR/Granger, walk-forward ML validation and feature importance. Sheet 10 provides formula-driven efficacy and backtest statistics with point-in-time outcomes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>7. Limitations</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>The sample contains only 24 quarters, so confidence intervals are wide. Weights, thresholds and calibration parameters are design judgments selected with knowledge of the full sample; they were not optimized out of sample. The latest quarter may be PROVISIONAL until all quarter-end sources are complete.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>8. How to audit this workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>Start at sheet 00, trace its formulas to sheet 05, then follow raw composite links through sheets 04, 03 and 02. Confirm parameters on sheet 01, model evidence on sheets 06–09, backtest formulas on sheet 10, and provenance on sheet 11. The yellow cells are formulas; verify_workbook_accuracy.py independently evaluates and reconciles them.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00047857"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>MÔ HÌNH ĐỊNH LƯỢNG VN-INDEX — PHƯƠNG PHÁP &amp; CÁCH DIỄN GIẢI</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Hướng dẫn tiếng Việt | phạm vi, kỷ luật point-in-time, kiến trúc, hiệu chỉnh, kiểm định và kiểm toán</t>
+        </is>
+      </c>
+    </row>
+    <row r="3"/>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>ẢNH CHỤP TRỰC TIẾP — LIÊN KẾT BẰNG CÔNG THỨC TỚI DASHBOARD</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="38" t="inlineStr">
+        <is>
+          <t>Quý mới nhất</t>
+        </is>
+      </c>
+      <c r="B5" s="39">
+        <f>'00_Executive_Dashboard'!A6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="38" t="inlineStr">
+        <is>
+          <t>Hành động hiệu chỉnh</t>
+        </is>
+      </c>
+      <c r="B6" s="39">
+        <f>'00_Executive_Dashboard'!B6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="38" t="inlineStr">
+        <is>
+          <t>Điểm hiệu chỉnh</t>
+        </is>
+      </c>
+      <c r="B7" s="40">
+        <f>'00_Executive_Dashboard'!C6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="38" t="inlineStr">
+        <is>
+          <t>Tỷ trọng cổ phiếu</t>
+        </is>
+      </c>
+      <c r="B8" s="39">
+        <f>'00_Executive_Dashboard'!D6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="38" t="inlineStr">
+        <is>
+          <t>Điểm tổng hợp thô</t>
+        </is>
+      </c>
+      <c r="B9" s="40">
+        <f>'00_Executive_Dashboard'!E6</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10"/>
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="41" t="inlineStr">
+        <is>
+          <t>1. Mô hình cho ra cái gì</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="42" customHeight="1">
+      <c r="A13" s="42" t="inlineStr">
+        <is>
+          <t>Đầu ra là điểm thế trận phân bổ theo quý và hành động danh mục tương ứng. Đây KHÔNG phải dự báo lợi suất và KHÔNG phải xác suất thị trường sụp đổ. Mô hình là công cụ hỗ trợ quyết định có kỷ luật, không phải khuyến nghị đầu tư.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14"/>
+    <row r="15">
+      <c r="A15" s="41" t="inlineStr">
+        <is>
+          <t>2. Dữ liệu và kỷ luật point-in-time</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="42" customHeight="1">
+      <c r="A16" s="42" t="inlineStr">
+        <is>
+          <t>Đầu vào gồm OHLCV VN-Index, vốn hóa HOSE, dòng vốn ngoại VNDirect api-finfo v4 cho STOCK_HOSE và ETF_HOSE, ADTV, đường cong lợi suất TPCP Việt Nam khớp Nelson-Siegel, cùng M2 từ ADB KIDB (nguồn SBV) nối với công bố GSO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="42" customHeight="1">
+      <c r="A17" s="42" t="inlineStr">
+        <is>
+          <t>Mỗi quý chỉ dùng thông tin đã có tại ngày ra quyết định. Nếu nguồn bắt buộc gặp lỗi, hệ thống dừng công bố; mô hình không âm thầm thay bằng dữ liệu bịa đặt hoặc giá trị mặc định.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="A19" s="41" t="inlineStr">
+        <is>
+          <t>3. Kiến trúc sáu trụ cột</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="42" customHeight="1">
+      <c r="A20" s="42" t="inlineStr">
+        <is>
+          <t>Vĩ mô &amp; Tiền tệ 25%; Toàn cầu &amp; Liên thị trường 20%; Định giá &amp; Đòn bẩy 20%; Mô hình Kinh tế lượng 15%; Học máy 10%; Cấu trúc Thị trường 10%. Các phần có trọng số cộng thành điểm tổng hợp thô.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21"/>
+    <row r="22">
+      <c r="A22" s="41" t="inlineStr">
+        <is>
+          <t>4. Hiệu chỉnh v2</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="42" customHeight="1">
+      <c r="A23" s="42" t="inlineStr">
+        <is>
+          <t>Bốn quý đầu giữ nguyên điểm thô. Sau đó chỉ dùng lịch sử trước quý hiện tại: z = (raw − prior_mean) / max(prior_std, min_std); winsorise z tại ±z_cap; calibrated = center + z_scale × z; cắt trong [clip_low, clip_high] và ràng buộc khoảng cách so với điểm thô bởi max_dist_from_raw.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="42" customHeight="1">
+      <c r="A24" s="42" t="inlineStr">
+        <is>
+          <t>Tham số SCORE_CALIBRATION: center 50, z_scale 15, min_history 4, min_std 5.0, z_cap 3.0, max_dist_from_raw 25.0, clip 0–100. Sàn min_std ngăn độ phân tán mẫu nhỏ làm phóng đại z; z_cap hạn chế sức chi phối của ngoại lệ; max_dist_from_raw ngăn tín hiệu hành động lệch phi lý khỏi bằng chứng thô. Ba chốt v2 này xử lý sự cố 2022-Q2 tụt về 0.00.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25"/>
+    <row r="26">
+      <c r="A26" s="41" t="inlineStr">
+        <is>
+          <t>5. Dải hành động</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="42" customHeight="1">
+      <c r="A27" s="42" t="inlineStr">
+        <is>
+          <t>80–100 BUY (85–100% cổ phiếu); 65–79.99 ACCUMULATE (70–85%); 50–64.99 HOLD (40–60%); 35–49.99 REDUCE (20–40%); 0–34.99 SELL (0–20%).</t>
+        </is>
+      </c>
+    </row>
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="41" t="inlineStr">
+        <is>
+          <t>6. Kiểm định và backtest</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="42" customHeight="1">
+      <c r="A30" s="42" t="inlineStr">
+        <is>
+          <t>Các sheet 06–09 trình bày hồi quy, VAR/Granger, kiểm định walk-forward cho ML và mức quan trọng đặc trưng. Sheet 10 cung cấp thống kê hiệu lực và backtest bằng công thức với kết quả point-in-time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="A32" s="41" t="inlineStr">
+        <is>
+          <t>7. Hạn chế</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="42" customHeight="1">
+      <c r="A33" s="42" t="inlineStr">
+        <is>
+          <t>Mẫu chỉ gồm 24 quý nên khoảng tin cậy rộng. Trọng số, ngưỡng và tham số hiệu chỉnh là phán định thiết kế khi đã biết toàn mẫu; chúng chưa được tối ưu ngoài mẫu. Quý mới nhất có thể ở trạng thái PROVISIONAL cho tới khi nguồn cuối quý hoàn tất.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34"/>
+    <row r="35">
+      <c r="A35" s="41" t="inlineStr">
+        <is>
+          <t>8. Cách kiểm toán workbook</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="42" customHeight="1">
+      <c r="A36" s="42" t="inlineStr">
+        <is>
+          <t>Bắt đầu ở sheet 00, lần theo công thức tới sheet 05, rồi lần điểm tổng hợp thô qua các sheet 04, 03 và 02. Đối chiếu tham số ở sheet 01, bằng chứng mô hình ở sheet 06–09, công thức backtest ở sheet 10 và nguồn gốc dữ liệu ở sheet 11. Ô màu vàng là công thức; verify_workbook_accuracy.py đánh giá độc lập và đối soát chúng.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="18">
+    <mergeCell ref="A24:F24"/>
+    <mergeCell ref="A16:F16"/>
+    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="A13:F13"/>
+    <mergeCell ref="A19:F19"/>
+    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A29:F29"/>
+    <mergeCell ref="A27:F27"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A17:F17"/>
+    <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A15:F15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>

--- a/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
+++ b/output/exports/VN_Index_Quant_Model_Complete_Architecture.xlsx
@@ -1134,7 +1134,7 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
-    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="27" customWidth="1" min="2" max="2"/>
     <col width="20" customWidth="1" min="3" max="3"/>
     <col width="22" customWidth="1" min="4" max="4"/>
     <col width="25" customWidth="1" min="5" max="5"/>
@@ -1196,7 +1196,7 @@
       </c>
       <c r="B6" s="13" t="inlineStr">
         <is>
-          <t>ema_20</t>
+          <t>m2_yoy_pct</t>
         </is>
       </c>
       <c r="C6" s="15" t="inlineStr">
@@ -1205,7 +1205,7 @@
         </is>
       </c>
       <c r="D6" s="34" t="n">
-        <v>0.02178040146827698</v>
+        <v>0.01707467995584011</v>
       </c>
       <c r="E6" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A6,$D$6:$D$20)</f>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>macd_line</t>
+          <t>bb_lower</t>
         </is>
       </c>
       <c r="C7" s="16" t="inlineStr">
@@ -1233,7 +1233,7 @@
         </is>
       </c>
       <c r="D7" s="36" t="n">
-        <v>0.02076428011059761</v>
+        <v>0.01457174587994814</v>
       </c>
       <c r="E7" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A7,$D$6:$D$20)</f>
@@ -1252,16 +1252,16 @@
       </c>
       <c r="B8" s="13" t="inlineStr">
         <is>
-          <t>etf_flow_q_zscore</t>
+          <t>ema_20</t>
         </is>
       </c>
       <c r="C8" s="15" t="inlineStr">
         <is>
-          <t>Flow / Structure</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D8" s="34" t="n">
-        <v>0.01783575303852558</v>
+        <v>0.01421605050563812</v>
       </c>
       <c r="E8" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A8,$D$6:$D$20)</f>
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="D9" s="36" t="n">
-        <v>0.01772940717637539</v>
+        <v>0.0133400084450841</v>
       </c>
       <c r="E9" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A9,$D$6:$D$20)</f>
@@ -1317,7 +1317,7 @@
         </is>
       </c>
       <c r="D10" s="34" t="n">
-        <v>0.01733604446053505</v>
+        <v>0.01314797159284353</v>
       </c>
       <c r="E10" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A10,$D$6:$D$20)</f>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>usd_vnd_zscore_lag1</t>
+          <t>us10y_zscore_1y</t>
         </is>
       </c>
       <c r="C11" s="16" t="inlineStr">
@@ -1345,7 +1345,7 @@
         </is>
       </c>
       <c r="D11" s="36" t="n">
-        <v>0.0167862419039011</v>
+        <v>0.01264037005603313</v>
       </c>
       <c r="E11" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A11,$D$6:$D$20)</f>
@@ -1364,16 +1364,16 @@
       </c>
       <c r="B12" s="13" t="inlineStr">
         <is>
-          <t>us10y_zscore_1y</t>
+          <t>oil_n_shock_days_ytd</t>
         </is>
       </c>
       <c r="C12" s="15" t="inlineStr">
         <is>
-          <t>Global / Rates</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D12" s="34" t="n">
-        <v>0.01557330787181854</v>
+        <v>0.01242248620837927</v>
       </c>
       <c r="E12" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A12,$D$6:$D$20)</f>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="B13" s="8" t="inlineStr">
         <is>
-          <t>oil_n_shock_days_ytd</t>
+          <t>macd_line</t>
         </is>
       </c>
       <c r="C13" s="16" t="inlineStr">
@@ -1401,7 +1401,7 @@
         </is>
       </c>
       <c r="D13" s="36" t="n">
-        <v>0.01539521757513285</v>
+        <v>0.01232288777828217</v>
       </c>
       <c r="E13" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A13,$D$6:$D$20)</f>
@@ -1420,16 +1420,16 @@
       </c>
       <c r="B14" s="13" t="inlineStr">
         <is>
-          <t>etf_flow_q_zscore_live</t>
+          <t>oil_max_weekly_change_ytd</t>
         </is>
       </c>
       <c r="C14" s="15" t="inlineStr">
         <is>
-          <t>Flow / Structure</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D14" s="34" t="n">
-        <v>0.01488733943551779</v>
+        <v>0.01212919689714909</v>
       </c>
       <c r="E14" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A14,$D$6:$D$20)</f>
@@ -1448,16 +1448,16 @@
       </c>
       <c r="B15" s="8" t="inlineStr">
         <is>
-          <t>dxy_zscore_60d</t>
+          <t>valuation_composite_score</t>
         </is>
       </c>
       <c r="C15" s="16" t="inlineStr">
         <is>
-          <t>Global / Rates</t>
+          <t>Technical / Market</t>
         </is>
       </c>
       <c r="D15" s="36" t="n">
-        <v>0.01360253803431988</v>
+        <v>0.01088140346109867</v>
       </c>
       <c r="E15" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A15,$D$6:$D$20)</f>
@@ -1476,7 +1476,7 @@
       </c>
       <c r="B16" s="13" t="inlineStr">
         <is>
-          <t>bb_lower</t>
+          <t>headline_pe</t>
         </is>
       </c>
       <c r="C16" s="15" t="inlineStr">
@@ -1485,7 +1485,7 @@
         </is>
       </c>
       <c r="D16" s="34" t="n">
-        <v>0.0134799899533391</v>
+        <v>0.01080580707639456</v>
       </c>
       <c r="E16" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A16,$D$6:$D$20)</f>
@@ -1504,16 +1504,16 @@
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>ex_vingroup_pe</t>
+          <t>dxy_zscore_60d</t>
         </is>
       </c>
       <c r="C17" s="16" t="inlineStr">
         <is>
-          <t>Technical / Market</t>
+          <t>Global / Rates</t>
         </is>
       </c>
       <c r="D17" s="36" t="n">
-        <v>0.01324111688882113</v>
+        <v>0.01069003902375698</v>
       </c>
       <c r="E17" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A17,$D$6:$D$20)</f>
@@ -1532,7 +1532,7 @@
       </c>
       <c r="B18" s="13" t="inlineStr">
         <is>
-          <t>nff_ex_etf_q_ytd</t>
+          <t>nff_ex_etf_rolling60d</t>
         </is>
       </c>
       <c r="C18" s="15" t="inlineStr">
@@ -1541,7 +1541,7 @@
         </is>
       </c>
       <c r="D18" s="34" t="n">
-        <v>0.01247525215148926</v>
+        <v>0.01060809195041656</v>
       </c>
       <c r="E18" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A18,$D$6:$D$20)</f>
@@ -1560,7 +1560,7 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>nff_ex_etf_rolling60d</t>
+          <t>price_vs_ma200</t>
         </is>
       </c>
       <c r="C19" s="16" t="inlineStr">
@@ -1569,7 +1569,7 @@
         </is>
       </c>
       <c r="D19" s="36" t="n">
-        <v>0.01242704410105944</v>
+        <v>0.01058133877813816</v>
       </c>
       <c r="E19" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A19,$D$6:$D$20)</f>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="B20" s="13" t="inlineStr">
         <is>
-          <t>rvol_10d</t>
+          <t>macd_signal</t>
         </is>
       </c>
       <c r="C20" s="15" t="inlineStr">
@@ -1597,7 +1597,7 @@
         </is>
       </c>
       <c r="D20" s="34" t="n">
-        <v>0.01225554849952459</v>
+        <v>0.01048300601541996</v>
       </c>
       <c r="E20" s="35">
         <f>SUMIF($A$6:$A$20,"&lt;="&amp;A20,$D$6:$D$20)</f>
@@ -5322,28 +5322,28 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
     <col width="27" customWidth="1" min="4" max="4"/>
-    <col width="11" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="11" customWidth="1" min="7" max="7"/>
-    <col width="11" customWidth="1" min="8" max="8"/>
-    <col width="11" customWidth="1" min="9" max="9"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="23" customWidth="1" min="6" max="6"/>
+    <col width="19" customWidth="1" min="7" max="7"/>
+    <col width="20" customWidth="1" min="8" max="8"/>
+    <col width="21" customWidth="1" min="9" max="9"/>
     <col width="11" customWidth="1" min="10" max="10"/>
-    <col width="11" customWidth="1" min="11" max="11"/>
-    <col width="11" customWidth="1" min="12" max="12"/>
-    <col width="11" customWidth="1" min="13" max="13"/>
-    <col width="11" customWidth="1" min="14" max="14"/>
-    <col width="11" customWidth="1" min="15" max="15"/>
-    <col width="11" customWidth="1" min="16" max="16"/>
+    <col width="20" customWidth="1" min="11" max="11"/>
+    <col width="19" customWidth="1" min="12" max="12"/>
+    <col width="21" customWidth="1" min="13" max="13"/>
+    <col width="21" customWidth="1" min="14" max="14"/>
+    <col width="21" customWidth="1" min="15" max="15"/>
+    <col width="19" customWidth="1" min="16" max="16"/>
     <col width="22" customWidth="1" min="17" max="17"/>
     <col width="22" customWidth="1" min="18" max="18"/>
-    <col width="13" customWidth="1" min="19" max="19"/>
+    <col width="19" customWidth="1" min="19" max="19"/>
     <col width="23" customWidth="1" min="20" max="20"/>
     <col width="21" customWidth="1" min="21" max="21"/>
-    <col width="11" customWidth="1" min="22" max="22"/>
+    <col width="22" customWidth="1" min="22" max="22"/>
     <col width="13" customWidth="1" min="23" max="23"/>
     <col width="17" customWidth="1" min="24" max="24"/>
-    <col width="12" customWidth="1" min="25" max="25"/>
-    <col width="11" customWidth="1" min="26" max="26"/>
+    <col width="22" customWidth="1" min="25" max="25"/>
+    <col width="22" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -7332,7 +7332,7 @@
         <v>1860.01</v>
       </c>
       <c r="D27" s="22" t="n">
-        <v>1780.68</v>
+        <v>1768.62</v>
       </c>
       <c r="E27" s="23" t="n">
         <v>3.7228</v>
@@ -7409,64 +7409,66 @@
       </c>
       <c r="B28" s="13" t="inlineStr">
         <is>
-          <t>2026-09-25</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="C28" s="25" t="n">
-        <v>1780.68</v>
-      </c>
-      <c r="D28" s="25" t="n"/>
+        <v>1768.62</v>
+      </c>
+      <c r="D28" s="25" t="n">
+        <v>1749.3</v>
+      </c>
       <c r="E28" s="26" t="n">
-        <v>3.8615</v>
+        <v>3.824486217282372</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>0.004357</v>
+        <v>-0.006669987027570823</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>4.4753</v>
+        <v>4.490338434500489</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>0.5289</v>
+        <v>0.5641762386393379</v>
       </c>
       <c r="I28" s="26" t="n">
-        <v>-1.27</v>
+        <v>-1.2883999557269</v>
       </c>
       <c r="J28" s="26" t="n">
         <v>14.98</v>
       </c>
       <c r="K28" s="26" t="n">
-        <v>1.05</v>
+        <v>1.561003392211543</v>
       </c>
       <c r="L28" s="26" t="n">
-        <v>5.18</v>
+        <v>5.293000221252441</v>
       </c>
       <c r="M28" s="26" t="n">
-        <v>-0.0525</v>
+        <v>-0.1220948548235693</v>
       </c>
       <c r="N28" s="26" t="n">
-        <v>-0.1609</v>
+        <v>-0.1801222314895506</v>
       </c>
       <c r="O28" s="26" t="n">
-        <v>-0.16</v>
+        <v>-0.5758618955754176</v>
       </c>
       <c r="P28" s="26" t="n">
-        <v>43.8</v>
+        <v>43.81259366342714</v>
       </c>
       <c r="Q28" s="26" t="n">
-        <v>0.8055707548717673</v>
+        <v>0.7509441191245513</v>
       </c>
       <c r="R28" s="26" t="n">
-        <v>0.6810894520369312</v>
+        <v>0.638044654231649</v>
       </c>
       <c r="S28" s="26" t="n">
-        <v>20</v>
+        <v>20.39884195572824</v>
       </c>
       <c r="T28" s="26" t="n">
-        <v>-1.250996235356308</v>
+        <v>-1.222708307670604</v>
       </c>
       <c r="U28" s="26" t="n"/>
       <c r="V28" s="27" t="n">
-        <v>-0.119329</v>
+        <v>-0.1226154130605057</v>
       </c>
       <c r="W28" s="15" t="inlineStr">
         <is>
@@ -7474,13 +7476,13 @@
         </is>
       </c>
       <c r="X28" s="15" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y28" s="26" t="n">
-        <v>-0.1187</v>
+        <v>-0.1147552691905312</v>
       </c>
       <c r="Z28" s="27" t="n">
-        <v>0.0011</v>
+        <v>0.001304077894212551</v>
       </c>
     </row>
   </sheetData>
@@ -14179,8 +14181,8 @@
     <col width="12" customWidth="1" min="2" max="2"/>
     <col width="14" customWidth="1" min="3" max="3"/>
     <col width="21" customWidth="1" min="4" max="4"/>
-    <col width="13" customWidth="1" min="5" max="5"/>
-    <col width="16" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="25" customWidth="1" min="6" max="6"/>
     <col width="15" customWidth="1" min="7" max="7"/>
     <col width="14" customWidth="1" min="8" max="8"/>
   </cols>
@@ -14945,13 +14947,13 @@
         <v>2130</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.1342</v>
+        <v>0.08520704799252052</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.1092</v>
+        <v>0.06020704799252052</v>
       </c>
       <c r="F28" s="33" t="n">
-        <v>-0.0005999999999999999</v>
+        <v>-0.0002370158183153296</v>
       </c>
       <c r="G28" s="10">
         <f>MIN(10,E28*10)</f>
@@ -14987,7 +14989,7 @@
     <col width="11" customWidth="1" min="7" max="7"/>
     <col width="11" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
-    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="24" customWidth="1" min="10" max="10"/>
     <col width="18" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
@@ -15891,26 +15893,26 @@
         <v>2</v>
       </c>
       <c r="D28" s="26" t="n">
-        <v>0.0072</v>
+        <v>0</v>
       </c>
       <c r="E28" s="26" t="n">
-        <v>0.4775</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="F28" s="26" t="n">
-        <v>0.5699</v>
+        <v>0.3701</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>0.6359</v>
+        <v>0.725</v>
       </c>
       <c r="H28" s="26" t="n">
-        <v>0.9498</v>
+        <v>0.7961</v>
       </c>
       <c r="I28" s="12">
         <f>COUNTIF(D28:H28,"&lt;0.05")</f>
         <v/>
       </c>
       <c r="J28" s="33" t="n">
-        <v>0.0011</v>
+        <v>0.0001465826227169615</v>
       </c>
       <c r="K28" s="10">
         <f>MIN(100,MAX(0,50+J28*'01_Model_Config'!$B$33))</f>
@@ -17100,13 +17102,13 @@
         <v>8</v>
       </c>
       <c r="E28" s="15" t="n">
-        <v>104</v>
+        <v>136</v>
       </c>
       <c r="F28" s="27" t="n">
-        <v>0.425</v>
+        <v>0.4846</v>
       </c>
       <c r="G28" s="26" t="n">
-        <v>0.3692</v>
+        <v>0.4326</v>
       </c>
       <c r="H28" s="15" t="n">
         <v>-1</v>
@@ -17117,7 +17119,7 @@
         </is>
       </c>
       <c r="J28" s="27" t="n">
-        <v>0.5031</v>
+        <v>0.6264999999999999</v>
       </c>
       <c r="K28" s="10">
         <f>MIN(100,MAX(0,(F28+G28)/2*100))</f>
